--- a/crm/v2/eva-questions.xlsx
+++ b/crm/v2/eva-questions.xlsx
@@ -811,7 +811,7 @@
         <v/>
       </c>
       <c r="C14" s="7">
-        <f>COUNT('Клиентки (кастдев)'!A58:A102)</f>
+        <f>COUNT('Клиентки (кастдев)'!A58:A80)</f>
         <v/>
       </c>
       <c r="D14" s="7">
@@ -963,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U108"/>
+  <dimension ref="A1:U86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>Готова созвониться на 30 минут в Zoom? Нам очень важно твоё мнение</t>
+          <t>Готова созвониться в Zoom на 40 минут? Нам очень важно твоё мнение</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
@@ -3113,7 +3113,7 @@
       <c r="A54" s="12" t="n"/>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>2. ИНТЕРВЬЮ — открытые вопросы для Zoom, 20–30 минут. Записывайте коротко, своими словами</t>
+          <t>2. ИНТЕРВЬЮ — открытые вопросы для Zoom, 40 минут по плану (минуты — у каждого раздела). Записывайте коротко, своими словами</t>
         </is>
       </c>
       <c r="C54" s="12" t="n"/>
@@ -3216,7 +3216,7 @@
       <c r="A57" s="14" t="n"/>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Знакомство · 1</t>
+          <t>Знакомство и точка А · 4 · 7 мин</t>
         </is>
       </c>
       <c r="C57" s="14" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>Кем ты работаешь? Расскажи коротко, чем занимаешься.</t>
+          <t>Расскажи коротко о себе: чем занимаешься и как обычно выглядит твой день?</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D58" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Какая нагрузка и сколько свободы в дне</t>
+          <t>Зачем: Нагрузка, свобода в дне и где в нём паузы</t>
         </is>
       </c>
       <c r="E58" s="19">
@@ -3283,60 +3283,77 @@
       <c r="T58" s="21" t="n"/>
       <c r="U58" s="21" t="n"/>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="14" t="n"/>
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>Точка А · 3</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n"/>
-      <c r="D59" s="14" t="n"/>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="14" t="n"/>
-      <c r="H59" s="14" t="n"/>
-      <c r="I59" s="14" t="n"/>
-      <c r="J59" s="14" t="n"/>
-      <c r="K59" s="14" t="n"/>
-      <c r="L59" s="14" t="n"/>
-      <c r="M59" s="14" t="n"/>
-      <c r="N59" s="14" t="n"/>
-      <c r="O59" s="14" t="n"/>
-      <c r="P59" s="14" t="n"/>
-      <c r="Q59" s="14" t="n"/>
-      <c r="R59" s="14" t="n"/>
-      <c r="S59" s="14" t="n"/>
-      <c r="T59" s="14" t="n"/>
-      <c r="U59" s="14" t="n"/>
-    </row>
-    <row r="60" ht="71" customHeight="1">
-      <c r="A60" s="16" t="n">
+    <row r="59" ht="71" customHeight="1">
+      <c r="A59" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>Если бы твоя жизнь сейчас была погодой — какая это погода за окном?</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C59" s="18" t="inlineStr">
         <is>
           <t>Открытый ответ + метки</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>Зачем: Состояние одной картинкой. Отметьте погоду кнопкой — она уйдёт в статистику
 Быстрые метки: Солнечно · Переменная облачность · Пасмурно · Дождь · Гроза · Туман · Снег и тишина · Ветер, всё меняется</t>
         </is>
       </c>
+      <c r="E59" s="19">
+        <f>COUNTA(G59:U59)</f>
+        <v/>
+      </c>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>Переменная облачность · Туман — не понимаю, куда иду и чего хочу.</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="21" t="n"/>
+      <c r="I59" s="21" t="n"/>
+      <c r="J59" s="21" t="n"/>
+      <c r="K59" s="21" t="n"/>
+      <c r="L59" s="21" t="n"/>
+      <c r="M59" s="21" t="n"/>
+      <c r="N59" s="21" t="n"/>
+      <c r="O59" s="21" t="n"/>
+      <c r="P59" s="21" t="n"/>
+      <c r="Q59" s="21" t="n"/>
+      <c r="R59" s="21" t="n"/>
+      <c r="S59" s="21" t="n"/>
+      <c r="T59" s="21" t="n"/>
+      <c r="U59" s="21" t="n"/>
+    </row>
+    <row r="60" ht="58" customHeight="1">
+      <c r="A60" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Что тебя сейчас беспокоит или забирает силы больше всего? Когда это было в последний раз?</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Открытый ответ</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>Зачем: Настоящая боль и конкретный случай, а не общие слова</t>
+        </is>
+      </c>
       <c r="E60" s="19">
         <f>COUNTA(G60:U60)</f>
         <v/>
       </c>
       <c r="F60" s="20" t="inlineStr">
         <is>
-          <t>Переменная облачность · Туман — не понимаю, куда иду и чего хочу.</t>
+          <t>Ругаю себя за всё: что мало с ребёнком, что поправилась, что не работаю.</t>
         </is>
       </c>
       <c r="G60" s="21" t="n"/>
@@ -3357,11 +3374,11 @@
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>Что тебя сейчас беспокоит больше всего?</t>
+          <t>Какой твой самый актуальный запрос на сегодня? Чего хочется добиться?</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
@@ -3371,7 +3388,7 @@
       </c>
       <c r="D61" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Настоящая боль своими словами</t>
+          <t>Зачем: С чем Ева должна помочь в первую очередь</t>
         </is>
       </c>
       <c r="E61" s="19">
@@ -3380,7 +3397,7 @@
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>Ругаю себя за всё: что мало с ребёнком, что поправилась, что не работаю.</t>
+          <t>Хочу перестать жить на автопилоте и найти 20 минут в день только для себя.</t>
         </is>
       </c>
       <c r="G61" s="21" t="n"/>
@@ -3399,84 +3416,84 @@
       <c r="T61" s="21" t="n"/>
       <c r="U61" s="21" t="n"/>
     </row>
-    <row r="62" ht="58" customHeight="1">
-      <c r="A62" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>Какой твой самый актуальный запрос на сегодня? Чего хочется добиться?</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="14" t="n"/>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>День и ритуалы · 3 · 8 мин</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n"/>
+      <c r="D62" s="14" t="n"/>
+      <c r="E62" s="14" t="n"/>
+      <c r="F62" s="14" t="n"/>
+      <c r="G62" s="14" t="n"/>
+      <c r="H62" s="14" t="n"/>
+      <c r="I62" s="14" t="n"/>
+      <c r="J62" s="14" t="n"/>
+      <c r="K62" s="14" t="n"/>
+      <c r="L62" s="14" t="n"/>
+      <c r="M62" s="14" t="n"/>
+      <c r="N62" s="14" t="n"/>
+      <c r="O62" s="14" t="n"/>
+      <c r="P62" s="14" t="n"/>
+      <c r="Q62" s="14" t="n"/>
+      <c r="R62" s="14" t="n"/>
+      <c r="S62" s="14" t="n"/>
+      <c r="T62" s="14" t="n"/>
+      <c r="U62" s="14" t="n"/>
+    </row>
+    <row r="63" ht="58" customHeight="1">
+      <c r="A63" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Как проходят первые полчаса после пробуждения? Успеваешь уделить время себе — или день сразу начинается с суеты?</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
         <is>
           <t>Открытый ответ</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: С чем Ева должна помочь в первую очередь</t>
-        </is>
-      </c>
-      <c r="E62" s="19">
-        <f>COUNTA(G62:U62)</f>
-        <v/>
-      </c>
-      <c r="F62" s="20" t="inlineStr">
-        <is>
-          <t>Хочу перестать жить на автопилоте и найти 20 минут в день только для себя.</t>
-        </is>
-      </c>
-      <c r="G62" s="21" t="n"/>
-      <c r="H62" s="21" t="n"/>
-      <c r="I62" s="21" t="n"/>
-      <c r="J62" s="21" t="n"/>
-      <c r="K62" s="21" t="n"/>
-      <c r="L62" s="21" t="n"/>
-      <c r="M62" s="21" t="n"/>
-      <c r="N62" s="21" t="n"/>
-      <c r="O62" s="21" t="n"/>
-      <c r="P62" s="21" t="n"/>
-      <c r="Q62" s="21" t="n"/>
-      <c r="R62" s="21" t="n"/>
-      <c r="S62" s="21" t="n"/>
-      <c r="T62" s="21" t="n"/>
-      <c r="U62" s="21" t="n"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="14" t="n"/>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>Утро и день · 6</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n"/>
-      <c r="D63" s="14" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="14" t="n"/>
-      <c r="G63" s="14" t="n"/>
-      <c r="H63" s="14" t="n"/>
-      <c r="I63" s="14" t="n"/>
-      <c r="J63" s="14" t="n"/>
-      <c r="K63" s="14" t="n"/>
-      <c r="L63" s="14" t="n"/>
-      <c r="M63" s="14" t="n"/>
-      <c r="N63" s="14" t="n"/>
-      <c r="O63" s="14" t="n"/>
-      <c r="P63" s="14" t="n"/>
-      <c r="Q63" s="14" t="n"/>
-      <c r="R63" s="14" t="n"/>
-      <c r="S63" s="14" t="n"/>
-      <c r="T63" s="14" t="n"/>
-      <c r="U63" s="14" t="n"/>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>Зачем: Есть ли окно для утренней практики и что уже радует</t>
+        </is>
+      </c>
+      <c r="E63" s="19">
+        <f>COUNTA(G63:U63)</f>
+        <v/>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>Сразу дети, завтраки, сборы. Кайфушка — душ с любимым гелем.</t>
+        </is>
+      </c>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+      <c r="J63" s="21" t="n"/>
+      <c r="K63" s="21" t="n"/>
+      <c r="L63" s="21" t="n"/>
+      <c r="M63" s="21" t="n"/>
+      <c r="N63" s="21" t="n"/>
+      <c r="O63" s="21" t="n"/>
+      <c r="P63" s="21" t="n"/>
+      <c r="Q63" s="21" t="n"/>
+      <c r="R63" s="21" t="n"/>
+      <c r="S63" s="21" t="n"/>
+      <c r="T63" s="21" t="n"/>
+      <c r="U63" s="21" t="n"/>
     </row>
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>Что ты делаешь в первые 15–30 минут после пробуждения? Есть любимые утренние ритуалы, свои «кайфушки»?</t>
+          <t>Бывают ли паузы в течение дня? Чем ты их заполняешь — Reels, подкасты, музыка, прогулка?</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
@@ -3486,7 +3503,7 @@
       </c>
       <c r="D64" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Окно для утренней практики и что уже радует</t>
+          <t>Зачем: С чем Ева конкурирует за 5 минут внимания и где к месту аудио</t>
         </is>
       </c>
       <c r="E64" s="19">
@@ -3495,7 +3512,7 @@
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>Сразу дети, завтраки, сборы. Кайфушка — душ с любимым гелем.</t>
+          <t>Гуляю с коляской — это и есть пауза, слушаю подкасты.</t>
         </is>
       </c>
       <c r="G64" s="21" t="n"/>
@@ -3516,11 +3533,11 @@
     </row>
     <row r="65" ht="58" customHeight="1">
       <c r="A65" s="16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>Что повышает тебе настроение?</t>
+          <t>Какой у тебя реальный вечер и каким был бы идеальный? Что помогает переключиться и легко уснуть?</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
@@ -3530,7 +3547,7 @@
       </c>
       <c r="D65" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Источники радости — для контента и пушей</t>
+          <t>Зачем: Ритуалы перехода и сон: нужен ли вечерний ритуал</t>
         </is>
       </c>
       <c r="E65" s="19">
@@ -3539,7 +3556,7 @@
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>Разговор с подругой и что-то новое — книга, место.</t>
+          <t>Идеальный — ужин с мужем без телефонов. Реальный — каждый в своём экране.</t>
         </is>
       </c>
       <c r="G65" s="21" t="n"/>
@@ -3558,49 +3575,32 @@
       <c r="T65" s="21" t="n"/>
       <c r="U65" s="21" t="n"/>
     </row>
-    <row r="66" ht="58" customHeight="1">
-      <c r="A66" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>Успеваешь уделять время себе утром — или день сразу начинается с суеты?</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D66" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Есть ли место для утренней программы</t>
-        </is>
-      </c>
-      <c r="E66" s="19">
-        <f>COUNTA(G66:U66)</f>
-        <v/>
-      </c>
-      <c r="F66" s="20" t="inlineStr">
-        <is>
-          <t>Нет, день сразу начинается с суеты.</t>
-        </is>
-      </c>
-      <c r="G66" s="21" t="n"/>
-      <c r="H66" s="21" t="n"/>
-      <c r="I66" s="21" t="n"/>
-      <c r="J66" s="21" t="n"/>
-      <c r="K66" s="21" t="n"/>
-      <c r="L66" s="21" t="n"/>
-      <c r="M66" s="21" t="n"/>
-      <c r="N66" s="21" t="n"/>
-      <c r="O66" s="21" t="n"/>
-      <c r="P66" s="21" t="n"/>
-      <c r="Q66" s="21" t="n"/>
-      <c r="R66" s="21" t="n"/>
-      <c r="S66" s="21" t="n"/>
-      <c r="T66" s="21" t="n"/>
-      <c r="U66" s="21" t="n"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="14" t="n"/>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Ресурсы: чего хватает и не хватает · 4 · 8 мин</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="n"/>
+      <c r="D66" s="14" t="n"/>
+      <c r="E66" s="14" t="n"/>
+      <c r="F66" s="14" t="n"/>
+      <c r="G66" s="14" t="n"/>
+      <c r="H66" s="14" t="n"/>
+      <c r="I66" s="14" t="n"/>
+      <c r="J66" s="14" t="n"/>
+      <c r="K66" s="14" t="n"/>
+      <c r="L66" s="14" t="n"/>
+      <c r="M66" s="14" t="n"/>
+      <c r="N66" s="14" t="n"/>
+      <c r="O66" s="14" t="n"/>
+      <c r="P66" s="14" t="n"/>
+      <c r="Q66" s="14" t="n"/>
+      <c r="R66" s="14" t="n"/>
+      <c r="S66" s="14" t="n"/>
+      <c r="T66" s="14" t="n"/>
+      <c r="U66" s="14" t="n"/>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" s="16" t="n">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>Опиши свой обычный день от обеда до вечера.</t>
+          <t>В какие моменты ты чувствуешь себя максимально счастливой и наполненной? Что поднимает настроение?</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="D67" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Где в дне паузы и свободные минуты</t>
+          <t>Зачем: Откуда берётся ресурс — для контента и пушей</t>
         </is>
       </c>
       <c r="E67" s="19">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>Работаю до семи, дорога час, вечером готовлю на завтра.</t>
+          <t>Когда занимаюсь спортом — потом весь день другой.</t>
         </is>
       </c>
       <c r="G67" s="21" t="n"/>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>Бывают ли у тебя паузы в течение дня? Чем ты их заполняешь — Reels, чай, прогулка?</t>
+          <t>Чего тебе больше всего не хватает в повседневной жизни? Если бы появился лишний час только для себя — на что бы ты его потратила?</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="D68" s="18" t="inlineStr">
         <is>
-          <t>Зачем: С чем Ева конкурирует за 5 минут внимания</t>
+          <t>Зачем: Дефицит, который Ева может закрыть, и желаемое поведение</t>
         </is>
       </c>
       <c r="E68" s="19">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>Гуляю с коляской — это и есть пауза, слушаю подкасты.</t>
+          <t>Дисциплины — всё начинаю и бросаю.</t>
         </is>
       </c>
       <c r="G68" s="21" t="n"/>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>В какие моменты ты слушаешь подкасты или музыку?</t>
+          <t>Когда ты последний раз специально делала что-то для себя — практику, спорт, курс? Как это было, почему продолжила или бросила?</t>
         </is>
       </c>
       <c r="C69" s="18" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D69" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Где к месту аудиопрактики</t>
+          <t>Зачем: Реальное поведение, а не намерения</t>
         </is>
       </c>
       <c r="E69" s="19">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>В машине и на прогулке с собакой.</t>
+          <t>Месяц назад ходила на пилатес, потом отпуск — и выпала.</t>
         </is>
       </c>
       <c r="G69" s="21" t="n"/>
@@ -3734,76 +3734,76 @@
       <c r="T69" s="21" t="n"/>
       <c r="U69" s="21" t="n"/>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="14" t="n"/>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>Вечер и сон · 3</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="n"/>
-      <c r="D70" s="14" t="n"/>
-      <c r="E70" s="14" t="n"/>
-      <c r="F70" s="14" t="n"/>
-      <c r="G70" s="14" t="n"/>
-      <c r="H70" s="14" t="n"/>
-      <c r="I70" s="14" t="n"/>
-      <c r="J70" s="14" t="n"/>
-      <c r="K70" s="14" t="n"/>
-      <c r="L70" s="14" t="n"/>
-      <c r="M70" s="14" t="n"/>
-      <c r="N70" s="14" t="n"/>
-      <c r="O70" s="14" t="n"/>
-      <c r="P70" s="14" t="n"/>
-      <c r="Q70" s="14" t="n"/>
-      <c r="R70" s="14" t="n"/>
-      <c r="S70" s="14" t="n"/>
-      <c r="T70" s="14" t="n"/>
-      <c r="U70" s="14" t="n"/>
-    </row>
-    <row r="71" ht="58" customHeight="1">
-      <c r="A71" s="16" t="n">
+    <row r="70" ht="58" customHeight="1">
+      <c r="A70" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>Легко ли тебе уснуть? Что мешает?</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>Какими приложениями, каналами или курсами «про себя» пользуешься? За что за последний год платила — и за что было не жалко денег?</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
         <is>
           <t>Открытый ответ</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Сон — частая боль: нужен ли вечерний ритуал</t>
-        </is>
-      </c>
-      <c r="E71" s="19">
-        <f>COUNTA(G71:U71)</f>
-        <v/>
-      </c>
-      <c r="F71" s="20" t="inlineStr">
-        <is>
-          <t>Падаю и сразу сплю, но просыпаюсь ночью.</t>
-        </is>
-      </c>
-      <c r="G71" s="21" t="n"/>
-      <c r="H71" s="21" t="n"/>
-      <c r="I71" s="21" t="n"/>
-      <c r="J71" s="21" t="n"/>
-      <c r="K71" s="21" t="n"/>
-      <c r="L71" s="21" t="n"/>
-      <c r="M71" s="21" t="n"/>
-      <c r="N71" s="21" t="n"/>
-      <c r="O71" s="21" t="n"/>
-      <c r="P71" s="21" t="n"/>
-      <c r="Q71" s="21" t="n"/>
-      <c r="R71" s="21" t="n"/>
-      <c r="S71" s="21" t="n"/>
-      <c r="T71" s="21" t="n"/>
-      <c r="U71" s="21" t="n"/>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>Зачем: Конкуренты, реальный чек и за что платят</t>
+        </is>
+      </c>
+      <c r="E70" s="19">
+        <f>COUNTA(G70:U70)</f>
+        <v/>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>Последний раз купила курс за 7 900 — прошла половину.</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="n"/>
+      <c r="H70" s="21" t="n"/>
+      <c r="I70" s="21" t="n"/>
+      <c r="J70" s="21" t="n"/>
+      <c r="K70" s="21" t="n"/>
+      <c r="L70" s="21" t="n"/>
+      <c r="M70" s="21" t="n"/>
+      <c r="N70" s="21" t="n"/>
+      <c r="O70" s="21" t="n"/>
+      <c r="P70" s="21" t="n"/>
+      <c r="Q70" s="21" t="n"/>
+      <c r="R70" s="21" t="n"/>
+      <c r="S70" s="21" t="n"/>
+      <c r="T70" s="21" t="n"/>
+      <c r="U70" s="21" t="n"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="14" t="n"/>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Контент и приложения · 2 · 6 мин</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="n"/>
+      <c r="D71" s="14" t="n"/>
+      <c r="E71" s="14" t="n"/>
+      <c r="F71" s="14" t="n"/>
+      <c r="G71" s="14" t="n"/>
+      <c r="H71" s="14" t="n"/>
+      <c r="I71" s="14" t="n"/>
+      <c r="J71" s="14" t="n"/>
+      <c r="K71" s="14" t="n"/>
+      <c r="L71" s="14" t="n"/>
+      <c r="M71" s="14" t="n"/>
+      <c r="N71" s="14" t="n"/>
+      <c r="O71" s="14" t="n"/>
+      <c r="P71" s="14" t="n"/>
+      <c r="Q71" s="14" t="n"/>
+      <c r="R71" s="14" t="n"/>
+      <c r="S71" s="14" t="n"/>
+      <c r="T71" s="14" t="n"/>
+      <c r="U71" s="14" t="n"/>
     </row>
     <row r="72" ht="58" customHeight="1">
       <c r="A72" s="16" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>Как выглядит твой идеальный вечер — и как реальный?</t>
+          <t>Какое приложение на телефоне твоё любимое и почему? А из-за чего приложения раздражают — что заставляет удалить, какие пуши бесят?</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="D72" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Разрыв между желаемым и тем, как есть</t>
+          <t>Зачем: Ориентир по удобству и чего не делать в Еве</t>
         </is>
       </c>
       <c r="E72" s="19">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>Идеальный — ужин с мужем без телефонов. Реальный — каждый в своём экране.</t>
+          <t>Duolingo: маленькие шаги и стрик, приятно не терять.</t>
         </is>
       </c>
       <c r="G72" s="21" t="n"/>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>Что помогает тебе переключиться с работы и семьи на отдых?</t>
+          <t>Что помогает не просто посмотреть урок, а внедрить совет в жизнь — трекеры, задания, напоминания? Возвращаешься к сохранённому «на потом»?</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D73" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Готовые ритуалы перехода</t>
+          <t>Зачем: Механика внедрения в программе и нужна ли «Моя полка»</t>
         </is>
       </c>
       <c r="E73" s="19">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>Душ и смена одежды — как ритуал «работа закончилась».</t>
+          <t>Задание на день и галочка, что сделала.</t>
         </is>
       </c>
       <c r="G73" s="21" t="n"/>
@@ -3897,7 +3897,7 @@
       <c r="A74" s="14" t="n"/>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Ресурсы: чего хватает и не хватает · 8</t>
+          <t>Эксперты и формат · 3 · 6 мин</t>
         </is>
       </c>
       <c r="C74" s="14" t="n"/>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>В какие моменты дня или недели ты чувствуешь себя максимально счастливой и наполненной?</t>
+          <t>Как ты выбираешь «своего» эксперта и понимаешь, что ему можно доверять? Кого слушаешь регулярно — за что ценишь?</t>
         </is>
       </c>
       <c r="C75" s="18" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="D75" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Откуда берётся ресурс</t>
+          <t>Зачем: Как подбирать и показывать экспертов, кого звать</t>
         </is>
       </c>
       <c r="E75" s="19">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>Когда занимаюсь спортом — потом весь день другой.</t>
+          <t>Смотрю на образование и живые отзывы, а не на количество подписчиков.</t>
         </is>
       </c>
       <c r="G75" s="21" t="n"/>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>Что сейчас больше всего забирает твои силы или настроение? Когда это было в последний раз?</t>
+          <t>Опиши идеальный урок для себя: где снят, сколько длится, как говорит спикер? Что цепляет быстрее — красивый кадр или живой разбор?</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D76" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Конкретный случай, а не общие слова</t>
+          <t>Зачем: Бриф для съёмок и визуальный стиль</t>
         </is>
       </c>
       <c r="E76" s="19">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>Бытовые мелочи, которые никто кроме меня не видит.</t>
+          <t>Как разговор с подругой, без пафоса, 15 минут максимум.</t>
         </is>
       </c>
       <c r="G76" s="21" t="n"/>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>Когда ты последний раз специально делала что-то для себя — практику, спорт, курс? Как это было?</t>
+          <t>Представь, что в приложении всего 3 раздела. Без каких тем ты бы его точно не скачала?</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D77" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Реальное поведение, а не намерения</t>
+          <t>Зачем: Ядро продукта</t>
         </is>
       </c>
       <c r="E77" s="19">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>Месяц назад ходила на пилатес, потом отпуск — и выпала.</t>
+          <t>Отношения, деньги, энергия.</t>
         </is>
       </c>
       <c r="G77" s="21" t="n"/>
@@ -4052,57 +4052,40 @@
       <c r="T77" s="21" t="n"/>
       <c r="U77" s="21" t="n"/>
     </row>
-    <row r="78" ht="58" customHeight="1">
-      <c r="A78" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>Какими приложениями, каналами или курсами «про себя» ты пользуешься? За что платила последний раз и сколько?</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Конкуренты и реальный чек</t>
-        </is>
-      </c>
-      <c r="E78" s="19">
-        <f>COUNTA(G78:U78)</f>
-        <v/>
-      </c>
-      <c r="F78" s="20" t="inlineStr">
-        <is>
-          <t>Последний раз купила курс за 7 900 — прошла половину.</t>
-        </is>
-      </c>
-      <c r="G78" s="21" t="n"/>
-      <c r="H78" s="21" t="n"/>
-      <c r="I78" s="21" t="n"/>
-      <c r="J78" s="21" t="n"/>
-      <c r="K78" s="21" t="n"/>
-      <c r="L78" s="21" t="n"/>
-      <c r="M78" s="21" t="n"/>
-      <c r="N78" s="21" t="n"/>
-      <c r="O78" s="21" t="n"/>
-      <c r="P78" s="21" t="n"/>
-      <c r="Q78" s="21" t="n"/>
-      <c r="R78" s="21" t="n"/>
-      <c r="S78" s="21" t="n"/>
-      <c r="T78" s="21" t="n"/>
-      <c r="U78" s="21" t="n"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="14" t="n"/>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Перемены и рекомендации · 2 · 3 мин</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="n"/>
+      <c r="D78" s="14" t="n"/>
+      <c r="E78" s="14" t="n"/>
+      <c r="F78" s="14" t="n"/>
+      <c r="G78" s="14" t="n"/>
+      <c r="H78" s="14" t="n"/>
+      <c r="I78" s="14" t="n"/>
+      <c r="J78" s="14" t="n"/>
+      <c r="K78" s="14" t="n"/>
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="14" t="n"/>
+      <c r="N78" s="14" t="n"/>
+      <c r="O78" s="14" t="n"/>
+      <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14" t="n"/>
+      <c r="R78" s="14" t="n"/>
+      <c r="S78" s="14" t="n"/>
+      <c r="T78" s="14" t="n"/>
+      <c r="U78" s="14" t="n"/>
     </row>
     <row r="79" ht="58" customHeight="1">
       <c r="A79" s="16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>Какая сфера твоей жизни сейчас закрыта лучше всего?</t>
+          <t>Вспомни момент, когда ты по-настоящему изменила привычку или взгляд на вещи. Что помогло — и как ты поняла, что изменения случились?</t>
         </is>
       </c>
       <c r="C79" s="18" t="inlineStr">
@@ -4112,7 +4095,7 @@
       </c>
       <c r="D79" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Опора, на которую можно строить</t>
+          <t>Зачем: Что запускает перемены и как измерять результат в Еве</t>
         </is>
       </c>
       <c r="E79" s="19">
@@ -4121,7 +4104,7 @@
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>Дружба: у меня классные подруги.</t>
+          <t>Начала бегать после разговора с врачом — испугалась.</t>
         </is>
       </c>
       <c r="G79" s="21" t="n"/>
@@ -4142,11 +4125,11 @@
     </row>
     <row r="80" ht="58" customHeight="1">
       <c r="A80" s="16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>За что ты благодарна своему нынешнему образу жизни?</t>
+          <t>Что должно произойти, чтобы ты сказала подруге «попробуй Еву»? Кому бы ты её посоветовала?</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
@@ -4156,7 +4139,7 @@
       </c>
       <c r="D80" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Что человек ценит и боится потерять</t>
+          <t>Зачем: Рекомендации и реферальная программа</t>
         </is>
       </c>
       <c r="E80" s="19">
@@ -4165,7 +4148,7 @@
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
-          <t>За гибкий график и то, что дети рядом.</t>
+          <t>Если реально поможет со сном — посоветую сестре и подругам из мамского чата.</t>
         </is>
       </c>
       <c r="G80" s="21" t="n"/>
@@ -4185,12 +4168,14 @@
       <c r="U80" s="21" t="n"/>
     </row>
     <row r="81" ht="58" customHeight="1">
-      <c r="A81" s="16" t="n">
-        <v>20</v>
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>Чего тебе больше всего не хватает в повседневной жизни — времени на себя, общения, эстетики, дисциплины, тишины?</t>
+          <t>Что ещё важного прозвучало</t>
         </is>
       </c>
       <c r="C81" s="18" t="inlineStr">
@@ -4200,18 +4185,14 @@
       </c>
       <c r="D81" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Дефицит, который Ева может закрыть</t>
+          <t>Всё, что не попало в вопросы</t>
         </is>
       </c>
       <c r="E81" s="19">
         <f>COUNTA(G81:U81)</f>
         <v/>
       </c>
-      <c r="F81" s="20" t="inlineStr">
-        <is>
-          <t>Дисциплины — всё начинаю и бросаю.</t>
-        </is>
-      </c>
+      <c r="F81" s="20" t="n"/>
       <c r="G81" s="21" t="n"/>
       <c r="H81" s="21" t="n"/>
       <c r="I81" s="21" t="n"/>
@@ -4228,94 +4209,90 @@
       <c r="T81" s="21" t="n"/>
       <c r="U81" s="21" t="n"/>
     </row>
-    <row r="82" ht="58" customHeight="1">
-      <c r="A82" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>Если бы в твоём дне появился лишний час только для себя — на что бы ты его потратила?</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D82" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Желаемое поведение — подсказка для программы</t>
-        </is>
-      </c>
-      <c r="E82" s="19">
-        <f>COUNTA(G82:U82)</f>
-        <v/>
-      </c>
-      <c r="F82" s="20" t="inlineStr">
-        <is>
-          <t>Почитала бы и помедитировала.</t>
-        </is>
-      </c>
-      <c r="G82" s="21" t="n"/>
-      <c r="H82" s="21" t="n"/>
-      <c r="I82" s="21" t="n"/>
-      <c r="J82" s="21" t="n"/>
-      <c r="K82" s="21" t="n"/>
-      <c r="L82" s="21" t="n"/>
-      <c r="M82" s="21" t="n"/>
-      <c r="N82" s="21" t="n"/>
-      <c r="O82" s="21" t="n"/>
-      <c r="P82" s="21" t="n"/>
-      <c r="Q82" s="21" t="n"/>
-      <c r="R82" s="21" t="n"/>
-      <c r="S82" s="21" t="n"/>
-      <c r="T82" s="21" t="n"/>
-      <c r="U82" s="21" t="n"/>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="14" t="n"/>
-      <c r="B83" s="15" t="inlineStr">
-        <is>
-          <t>Где и как смотрит контент · 7</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="n"/>
-      <c r="D83" s="14" t="n"/>
-      <c r="E83" s="14" t="n"/>
-      <c r="F83" s="14" t="n"/>
-      <c r="G83" s="14" t="n"/>
-      <c r="H83" s="14" t="n"/>
-      <c r="I83" s="14" t="n"/>
-      <c r="J83" s="14" t="n"/>
-      <c r="K83" s="14" t="n"/>
-      <c r="L83" s="14" t="n"/>
-      <c r="M83" s="14" t="n"/>
-      <c r="N83" s="14" t="n"/>
-      <c r="O83" s="14" t="n"/>
-      <c r="P83" s="14" t="n"/>
-      <c r="Q83" s="14" t="n"/>
-      <c r="R83" s="14" t="n"/>
-      <c r="S83" s="14" t="n"/>
-      <c r="T83" s="14" t="n"/>
-      <c r="U83" s="14" t="n"/>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="12" t="n"/>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>3. ИТОГ — сразу после созвона</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="n"/>
+      <c r="D82" s="12" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="12" t="n"/>
+      <c r="G82" s="12" t="n"/>
+      <c r="H82" s="12" t="n"/>
+      <c r="I82" s="12" t="n"/>
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="12" t="n"/>
+      <c r="M82" s="12" t="n"/>
+      <c r="N82" s="12" t="n"/>
+      <c r="O82" s="12" t="n"/>
+      <c r="P82" s="12" t="n"/>
+      <c r="Q82" s="12" t="n"/>
+      <c r="R82" s="12" t="n"/>
+      <c r="S82" s="12" t="n"/>
+      <c r="T82" s="12" t="n"/>
+      <c r="U82" s="12" t="n"/>
+    </row>
+    <row r="83" ht="84" customHeight="1">
+      <c r="A83" s="16" t="n"/>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>Что услышали (метки)</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>Несколько вариантов</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>⏳ Нет времени · 💸 Дорого · 📱 Неудобно в приложении · 🔔 Бесят пуши · 🎓 Хочет экспертов · 👭 Хочет сообщество · 🏠 Хочет офлайн · 🧘‍♀️ Любит короткие практики · 🌙 Проблемы со сном · 🤖 Нравится Ева-помощница · 💡 Идея фичи · ❤️ Готова рекомендовать</t>
+        </is>
+      </c>
+      <c r="E83" s="19">
+        <f>COUNTA(G83:U83)</f>
+        <v/>
+      </c>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t>⏳ Нет времени, 🧘‍♀️ Любит короткие практики, 🔔 Бесят пуши</t>
+        </is>
+      </c>
+      <c r="G83" s="21" t="n"/>
+      <c r="H83" s="21" t="n"/>
+      <c r="I83" s="21" t="n"/>
+      <c r="J83" s="21" t="n"/>
+      <c r="K83" s="21" t="n"/>
+      <c r="L83" s="21" t="n"/>
+      <c r="M83" s="21" t="n"/>
+      <c r="N83" s="21" t="n"/>
+      <c r="O83" s="21" t="n"/>
+      <c r="P83" s="21" t="n"/>
+      <c r="Q83" s="21" t="n"/>
+      <c r="R83" s="21" t="n"/>
+      <c r="S83" s="21" t="n"/>
+      <c r="T83" s="21" t="n"/>
+      <c r="U83" s="21" t="n"/>
     </row>
     <row r="84" ht="58" customHeight="1">
-      <c r="A84" s="16" t="n">
-        <v>22</v>
-      </c>
+      <c r="A84" s="16" t="n"/>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>Как ты смотришь полезный контент: выделяешь время и сидишь с блокнотом, включаешь фоном за готовкой или в зале, слушаешь в дороге?</t>
+          <t>Главный инсайт — одной фразой</t>
         </is>
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>Открытый ответ</t>
+          <t>Развёрнутый ответ</t>
         </is>
       </c>
       <c r="D84" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Как подавать: смотреть или слушать</t>
+          <t>Например: бросает практики, когда болеет ребёнок — нужен режим «пауза без чувства вины»</t>
         </is>
       </c>
       <c r="E84" s="19">
@@ -4324,7 +4301,7 @@
       </c>
       <c r="F84" s="20" t="inlineStr">
         <is>
-          <t>Слушаю в дороге и за готовкой, с блокнотом не сажусь никогда.</t>
+          <t>Бросает, когда пропускает пару дней и «сгорают» звёзды — нужен режим паузы без чувства вины.</t>
         </is>
       </c>
       <c r="G84" s="21" t="n"/>
@@ -4344,22 +4321,20 @@
       <c r="U84" s="21" t="n"/>
     </row>
     <row r="85" ht="58" customHeight="1">
-      <c r="A85" s="16" t="n">
-        <v>23</v>
-      </c>
+      <c r="A85" s="16" t="n"/>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>Вспомни своё самое любимое приложение на телефоне. Почему именно оно? За что ты его ценишь?</t>
+          <t>Что улучшить в Еве</t>
         </is>
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>Открытый ответ</t>
+          <t>Развёрнутый ответ</t>
         </is>
       </c>
       <c r="D85" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Ориентир по удобству</t>
+          <t>Идеи и просьбы</t>
         </is>
       </c>
       <c r="E85" s="19">
@@ -4368,7 +4343,7 @@
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>Duolingo: маленькие шаги и стрик, приятно не терять.</t>
+          <t>Режим «5 минут», пуши вечером, пауза для звёзд.</t>
         </is>
       </c>
       <c r="G85" s="21" t="n"/>
@@ -4387,23 +4362,21 @@
       <c r="T85" s="21" t="n"/>
       <c r="U85" s="21" t="n"/>
     </row>
-    <row r="86" ht="58" customHeight="1">
-      <c r="A86" s="16" t="n">
-        <v>24</v>
-      </c>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="16" t="n"/>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>Что тебя больше всего раздражает в приложениях — из-за чего сразу закрываешь или удаляешь?</t>
+          <t>Статус</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>Открытый ответ</t>
+          <t>Один вариант</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>Зачем: Чего не делать в Еве</t>
+          <t>Инсайты собраны · Готова помогать ещё</t>
         </is>
       </c>
       <c r="E86" s="19">
@@ -4412,7 +4385,7 @@
       </c>
       <c r="F86" s="20" t="inlineStr">
         <is>
-          <t>Сложно найти, где мои мастер-классы — много разделов.</t>
+          <t>Инсайты собраны</t>
         </is>
       </c>
       <c r="G86" s="21" t="n"/>
@@ -4430,896 +4403,6 @@
       <c r="S86" s="21" t="n"/>
       <c r="T86" s="21" t="n"/>
       <c r="U86" s="21" t="n"/>
-    </row>
-    <row r="87" ht="58" customHeight="1">
-      <c r="A87" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>Как ты относишься к push-уведомлениям? Какие бесят, а какие реально помогают?</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D87" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Пуши, которые не раздражают</t>
-        </is>
-      </c>
-      <c r="E87" s="19">
-        <f>COUNTA(G87:U87)</f>
-        <v/>
-      </c>
-      <c r="F87" s="20" t="inlineStr">
-        <is>
-          <t>Бесят «вернись к нам», помогают напоминания о том, что я сама поставила.</t>
-        </is>
-      </c>
-      <c r="G87" s="21" t="n"/>
-      <c r="H87" s="21" t="n"/>
-      <c r="I87" s="21" t="n"/>
-      <c r="J87" s="21" t="n"/>
-      <c r="K87" s="21" t="n"/>
-      <c r="L87" s="21" t="n"/>
-      <c r="M87" s="21" t="n"/>
-      <c r="N87" s="21" t="n"/>
-      <c r="O87" s="21" t="n"/>
-      <c r="P87" s="21" t="n"/>
-      <c r="Q87" s="21" t="n"/>
-      <c r="R87" s="21" t="n"/>
-      <c r="S87" s="21" t="n"/>
-      <c r="T87" s="21" t="n"/>
-      <c r="U87" s="21" t="n"/>
-    </row>
-    <row r="88" ht="58" customHeight="1">
-      <c r="A88" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>Бывает ли у тебя ощущение перегруза? Что его вызывает?</t>
-        </is>
-      </c>
-      <c r="C88" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D88" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Сколько контента — это уже много</t>
-        </is>
-      </c>
-      <c r="E88" s="19">
-        <f>COUNTA(G88:U88)</f>
-        <v/>
-      </c>
-      <c r="F88" s="20" t="inlineStr">
-        <is>
-          <t>Когда всё срочно и одновременно.</t>
-        </is>
-      </c>
-      <c r="G88" s="21" t="n"/>
-      <c r="H88" s="21" t="n"/>
-      <c r="I88" s="21" t="n"/>
-      <c r="J88" s="21" t="n"/>
-      <c r="K88" s="21" t="n"/>
-      <c r="L88" s="21" t="n"/>
-      <c r="M88" s="21" t="n"/>
-      <c r="N88" s="21" t="n"/>
-      <c r="O88" s="21" t="n"/>
-      <c r="P88" s="21" t="n"/>
-      <c r="Q88" s="21" t="n"/>
-      <c r="R88" s="21" t="n"/>
-      <c r="S88" s="21" t="n"/>
-      <c r="T88" s="21" t="n"/>
-      <c r="U88" s="21" t="n"/>
-    </row>
-    <row r="89" ht="58" customHeight="1">
-      <c r="A89" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>Сохраняешь ли ты полезное «на потом»? Как часто к нему возвращаешься?</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D89" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Нужна ли «Моя полка» и напоминания</t>
-        </is>
-      </c>
-      <c r="E89" s="19">
-        <f>COUNTA(G89:U89)</f>
-        <v/>
-      </c>
-      <c r="F89" s="20" t="inlineStr">
-        <is>
-          <t>Не сохраняю — либо сразу, либо никогда.</t>
-        </is>
-      </c>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
-      <c r="J89" s="21" t="n"/>
-      <c r="K89" s="21" t="n"/>
-      <c r="L89" s="21" t="n"/>
-      <c r="M89" s="21" t="n"/>
-      <c r="N89" s="21" t="n"/>
-      <c r="O89" s="21" t="n"/>
-      <c r="P89" s="21" t="n"/>
-      <c r="Q89" s="21" t="n"/>
-      <c r="R89" s="21" t="n"/>
-      <c r="S89" s="21" t="n"/>
-      <c r="T89" s="21" t="n"/>
-      <c r="U89" s="21" t="n"/>
-    </row>
-    <row r="90" ht="58" customHeight="1">
-      <c r="A90" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>Что помогает тебе не просто посмотреть урок, а реально внедрить совет в жизнь — трекеры, шпаргалки, задания?</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D90" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Механика внедрения в программе</t>
-        </is>
-      </c>
-      <c r="E90" s="19">
-        <f>COUNTA(G90:U90)</f>
-        <v/>
-      </c>
-      <c r="F90" s="20" t="inlineStr">
-        <is>
-          <t>Задание на день и галочка, что сделала.</t>
-        </is>
-      </c>
-      <c r="G90" s="21" t="n"/>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-      <c r="J90" s="21" t="n"/>
-      <c r="K90" s="21" t="n"/>
-      <c r="L90" s="21" t="n"/>
-      <c r="M90" s="21" t="n"/>
-      <c r="N90" s="21" t="n"/>
-      <c r="O90" s="21" t="n"/>
-      <c r="P90" s="21" t="n"/>
-      <c r="Q90" s="21" t="n"/>
-      <c r="R90" s="21" t="n"/>
-      <c r="S90" s="21" t="n"/>
-      <c r="T90" s="21" t="n"/>
-      <c r="U90" s="21" t="n"/>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="14" t="n"/>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t>Формат и эксперты · 6</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="n"/>
-      <c r="D91" s="14" t="n"/>
-      <c r="E91" s="14" t="n"/>
-      <c r="F91" s="14" t="n"/>
-      <c r="G91" s="14" t="n"/>
-      <c r="H91" s="14" t="n"/>
-      <c r="I91" s="14" t="n"/>
-      <c r="J91" s="14" t="n"/>
-      <c r="K91" s="14" t="n"/>
-      <c r="L91" s="14" t="n"/>
-      <c r="M91" s="14" t="n"/>
-      <c r="N91" s="14" t="n"/>
-      <c r="O91" s="14" t="n"/>
-      <c r="P91" s="14" t="n"/>
-      <c r="Q91" s="14" t="n"/>
-      <c r="R91" s="14" t="n"/>
-      <c r="S91" s="14" t="n"/>
-      <c r="T91" s="14" t="n"/>
-      <c r="U91" s="14" t="n"/>
-    </row>
-    <row r="92" ht="58" customHeight="1">
-      <c r="A92" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>Опиши идеальное обучающее видео для себя: где оно снято, сколько длится, как говорит спикер?</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D92" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Бриф для съёмок</t>
-        </is>
-      </c>
-      <c r="E92" s="19">
-        <f>COUNTA(G92:U92)</f>
-        <v/>
-      </c>
-      <c r="F92" s="20" t="inlineStr">
-        <is>
-          <t>Как разговор с подругой, без пафоса, 15 минут максимум.</t>
-        </is>
-      </c>
-      <c r="G92" s="21" t="n"/>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
-      <c r="J92" s="21" t="n"/>
-      <c r="K92" s="21" t="n"/>
-      <c r="L92" s="21" t="n"/>
-      <c r="M92" s="21" t="n"/>
-      <c r="N92" s="21" t="n"/>
-      <c r="O92" s="21" t="n"/>
-      <c r="P92" s="21" t="n"/>
-      <c r="Q92" s="21" t="n"/>
-      <c r="R92" s="21" t="n"/>
-      <c r="S92" s="21" t="n"/>
-      <c r="T92" s="21" t="n"/>
-      <c r="U92" s="21" t="n"/>
-    </row>
-    <row r="93" ht="58" customHeight="1">
-      <c r="A93" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>За какой контент — курсы, гайды, подписки, вебинары — за последний год тебе было совсем не жалко денег? Почему?</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D93" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: За что реально платят</t>
-        </is>
-      </c>
-      <c r="E93" s="19">
-        <f>COUNTA(G93:U93)</f>
-        <v/>
-      </c>
-      <c r="F93" s="20" t="inlineStr">
-        <is>
-          <t>Подписка на книги — слушаю каждый день.</t>
-        </is>
-      </c>
-      <c r="G93" s="21" t="n"/>
-      <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
-      <c r="J93" s="21" t="n"/>
-      <c r="K93" s="21" t="n"/>
-      <c r="L93" s="21" t="n"/>
-      <c r="M93" s="21" t="n"/>
-      <c r="N93" s="21" t="n"/>
-      <c r="O93" s="21" t="n"/>
-      <c r="P93" s="21" t="n"/>
-      <c r="Q93" s="21" t="n"/>
-      <c r="R93" s="21" t="n"/>
-      <c r="S93" s="21" t="n"/>
-      <c r="T93" s="21" t="n"/>
-      <c r="U93" s="21" t="n"/>
-    </row>
-    <row r="94" ht="58" customHeight="1">
-      <c r="A94" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>Как ты выбираешь «своего» эксперта? Как понимаешь, что ему можно доверять?</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D94" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Как подбирать и показывать экспертов</t>
-        </is>
-      </c>
-      <c r="E94" s="19">
-        <f>COUNTA(G94:U94)</f>
-        <v/>
-      </c>
-      <c r="F94" s="20" t="inlineStr">
-        <is>
-          <t>Смотрю на образование и живые отзывы, а не на количество подписчиков.</t>
-        </is>
-      </c>
-      <c r="G94" s="21" t="n"/>
-      <c r="H94" s="21" t="n"/>
-      <c r="I94" s="21" t="n"/>
-      <c r="J94" s="21" t="n"/>
-      <c r="K94" s="21" t="n"/>
-      <c r="L94" s="21" t="n"/>
-      <c r="M94" s="21" t="n"/>
-      <c r="N94" s="21" t="n"/>
-      <c r="O94" s="21" t="n"/>
-      <c r="P94" s="21" t="n"/>
-      <c r="Q94" s="21" t="n"/>
-      <c r="R94" s="21" t="n"/>
-      <c r="S94" s="21" t="n"/>
-      <c r="T94" s="21" t="n"/>
-      <c r="U94" s="21" t="n"/>
-    </row>
-    <row r="95" ht="58" customHeight="1">
-      <c r="A95" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Представь, что в приложении всего 3 раздела. Без каких тем ты бы его точно не скачала?</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D95" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Ядро продукта</t>
-        </is>
-      </c>
-      <c r="E95" s="19">
-        <f>COUNTA(G95:U95)</f>
-        <v/>
-      </c>
-      <c r="F95" s="20" t="inlineStr">
-        <is>
-          <t>Отношения, деньги, энергия.</t>
-        </is>
-      </c>
-      <c r="G95" s="21" t="n"/>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-      <c r="J95" s="21" t="n"/>
-      <c r="K95" s="21" t="n"/>
-      <c r="L95" s="21" t="n"/>
-      <c r="M95" s="21" t="n"/>
-      <c r="N95" s="21" t="n"/>
-      <c r="O95" s="21" t="n"/>
-      <c r="P95" s="21" t="n"/>
-      <c r="Q95" s="21" t="n"/>
-      <c r="R95" s="21" t="n"/>
-      <c r="S95" s="21" t="n"/>
-      <c r="T95" s="21" t="n"/>
-      <c r="U95" s="21" t="n"/>
-    </row>
-    <row r="96" ht="58" customHeight="1">
-      <c r="A96" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>На кого из известных женщин, спикеров или блогеров ты подписана и кого регулярно слушаешь? За что ты их ценишь?</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D96" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Кого звать в эксперты и амбассадоры</t>
-        </is>
-      </c>
-      <c r="E96" s="19">
-        <f>COUNTA(G96:U96)</f>
-        <v/>
-      </c>
-      <c r="F96" s="20" t="inlineStr">
-        <is>
-          <t>Слушаю Ирину Хакамаду — за спокойствие и опыт.</t>
-        </is>
-      </c>
-      <c r="G96" s="21" t="n"/>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
-      <c r="J96" s="21" t="n"/>
-      <c r="K96" s="21" t="n"/>
-      <c r="L96" s="21" t="n"/>
-      <c r="M96" s="21" t="n"/>
-      <c r="N96" s="21" t="n"/>
-      <c r="O96" s="21" t="n"/>
-      <c r="P96" s="21" t="n"/>
-      <c r="Q96" s="21" t="n"/>
-      <c r="R96" s="21" t="n"/>
-      <c r="S96" s="21" t="n"/>
-      <c r="T96" s="21" t="n"/>
-      <c r="U96" s="21" t="n"/>
-    </row>
-    <row r="97" ht="58" customHeight="1">
-      <c r="A97" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>Что быстрее привлекает твоё внимание: красивый «кинематографичный» кадр или динамичный разбор на доске или с презентацией?</t>
-        </is>
-      </c>
-      <c r="C97" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D97" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Визуальный стиль роликов</t>
-        </is>
-      </c>
-      <c r="E97" s="19">
-        <f>COUNTA(G97:U97)</f>
-        <v/>
-      </c>
-      <c r="F97" s="20" t="inlineStr">
-        <is>
-          <t>Красивый кадр цепляет, но остаюсь из-за смысла.</t>
-        </is>
-      </c>
-      <c r="G97" s="21" t="n"/>
-      <c r="H97" s="21" t="n"/>
-      <c r="I97" s="21" t="n"/>
-      <c r="J97" s="21" t="n"/>
-      <c r="K97" s="21" t="n"/>
-      <c r="L97" s="21" t="n"/>
-      <c r="M97" s="21" t="n"/>
-      <c r="N97" s="21" t="n"/>
-      <c r="O97" s="21" t="n"/>
-      <c r="P97" s="21" t="n"/>
-      <c r="Q97" s="21" t="n"/>
-      <c r="R97" s="21" t="n"/>
-      <c r="S97" s="21" t="n"/>
-      <c r="T97" s="21" t="n"/>
-      <c r="U97" s="21" t="n"/>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="14" t="n"/>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t>Механика трансформации · 2</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="n"/>
-      <c r="D98" s="14" t="n"/>
-      <c r="E98" s="14" t="n"/>
-      <c r="F98" s="14" t="n"/>
-      <c r="G98" s="14" t="n"/>
-      <c r="H98" s="14" t="n"/>
-      <c r="I98" s="14" t="n"/>
-      <c r="J98" s="14" t="n"/>
-      <c r="K98" s="14" t="n"/>
-      <c r="L98" s="14" t="n"/>
-      <c r="M98" s="14" t="n"/>
-      <c r="N98" s="14" t="n"/>
-      <c r="O98" s="14" t="n"/>
-      <c r="P98" s="14" t="n"/>
-      <c r="Q98" s="14" t="n"/>
-      <c r="R98" s="14" t="n"/>
-      <c r="S98" s="14" t="n"/>
-      <c r="T98" s="14" t="n"/>
-      <c r="U98" s="14" t="n"/>
-    </row>
-    <row r="99" ht="58" customHeight="1">
-      <c r="A99" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>Вспомни момент, когда ты по-настоящему изменила привычку или взгляд на вещи. Что именно тебе помогло?</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D99" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Что реально запускает перемены</t>
-        </is>
-      </c>
-      <c r="E99" s="19">
-        <f>COUNTA(G99:U99)</f>
-        <v/>
-      </c>
-      <c r="F99" s="20" t="inlineStr">
-        <is>
-          <t>Начала бегать после разговора с врачом — испугалась.</t>
-        </is>
-      </c>
-      <c r="G99" s="21" t="n"/>
-      <c r="H99" s="21" t="n"/>
-      <c r="I99" s="21" t="n"/>
-      <c r="J99" s="21" t="n"/>
-      <c r="K99" s="21" t="n"/>
-      <c r="L99" s="21" t="n"/>
-      <c r="M99" s="21" t="n"/>
-      <c r="N99" s="21" t="n"/>
-      <c r="O99" s="21" t="n"/>
-      <c r="P99" s="21" t="n"/>
-      <c r="Q99" s="21" t="n"/>
-      <c r="R99" s="21" t="n"/>
-      <c r="S99" s="21" t="n"/>
-      <c r="T99" s="21" t="n"/>
-      <c r="U99" s="21" t="n"/>
-    </row>
-    <row r="100" ht="58" customHeight="1">
-      <c r="A100" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>Как ты понимаешь, что прошла через трансформацию: изменилось состояние, появились результаты в деньгах или отношениях, стало легко на душе?</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D100" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Как измерять результат в Еве</t>
-        </is>
-      </c>
-      <c r="E100" s="19">
-        <f>COUNTA(G100:U100)</f>
-        <v/>
-      </c>
-      <c r="F100" s="20" t="inlineStr">
-        <is>
-          <t>Когда окружающие говорят, что я изменилась.</t>
-        </is>
-      </c>
-      <c r="G100" s="21" t="n"/>
-      <c r="H100" s="21" t="n"/>
-      <c r="I100" s="21" t="n"/>
-      <c r="J100" s="21" t="n"/>
-      <c r="K100" s="21" t="n"/>
-      <c r="L100" s="21" t="n"/>
-      <c r="M100" s="21" t="n"/>
-      <c r="N100" s="21" t="n"/>
-      <c r="O100" s="21" t="n"/>
-      <c r="P100" s="21" t="n"/>
-      <c r="Q100" s="21" t="n"/>
-      <c r="R100" s="21" t="n"/>
-      <c r="S100" s="21" t="n"/>
-      <c r="T100" s="21" t="n"/>
-      <c r="U100" s="21" t="n"/>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="14" t="n"/>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>Рекомендации · 1</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="n"/>
-      <c r="D101" s="14" t="n"/>
-      <c r="E101" s="14" t="n"/>
-      <c r="F101" s="14" t="n"/>
-      <c r="G101" s="14" t="n"/>
-      <c r="H101" s="14" t="n"/>
-      <c r="I101" s="14" t="n"/>
-      <c r="J101" s="14" t="n"/>
-      <c r="K101" s="14" t="n"/>
-      <c r="L101" s="14" t="n"/>
-      <c r="M101" s="14" t="n"/>
-      <c r="N101" s="14" t="n"/>
-      <c r="O101" s="14" t="n"/>
-      <c r="P101" s="14" t="n"/>
-      <c r="Q101" s="14" t="n"/>
-      <c r="R101" s="14" t="n"/>
-      <c r="S101" s="14" t="n"/>
-      <c r="T101" s="14" t="n"/>
-      <c r="U101" s="14" t="n"/>
-    </row>
-    <row r="102" ht="58" customHeight="1">
-      <c r="A102" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>Что должно произойти, чтобы ты сказала подруге «попробуй Еву»? Кому бы ты её посоветовала?</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D102" s="18" t="inlineStr">
-        <is>
-          <t>Зачем: Рекомендации и реферальная программа</t>
-        </is>
-      </c>
-      <c r="E102" s="19">
-        <f>COUNTA(G102:U102)</f>
-        <v/>
-      </c>
-      <c r="F102" s="20" t="inlineStr">
-        <is>
-          <t>Если реально поможет со сном — посоветую сестре и подругам из мамского чата.</t>
-        </is>
-      </c>
-      <c r="G102" s="21" t="n"/>
-      <c r="H102" s="21" t="n"/>
-      <c r="I102" s="21" t="n"/>
-      <c r="J102" s="21" t="n"/>
-      <c r="K102" s="21" t="n"/>
-      <c r="L102" s="21" t="n"/>
-      <c r="M102" s="21" t="n"/>
-      <c r="N102" s="21" t="n"/>
-      <c r="O102" s="21" t="n"/>
-      <c r="P102" s="21" t="n"/>
-      <c r="Q102" s="21" t="n"/>
-      <c r="R102" s="21" t="n"/>
-      <c r="S102" s="21" t="n"/>
-      <c r="T102" s="21" t="n"/>
-      <c r="U102" s="21" t="n"/>
-    </row>
-    <row r="103" ht="58" customHeight="1">
-      <c r="A103" s="16" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="B103" s="17" t="inlineStr">
-        <is>
-          <t>Что ещё важного прозвучало</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>Открытый ответ</t>
-        </is>
-      </c>
-      <c r="D103" s="18" t="inlineStr">
-        <is>
-          <t>Всё, что не попало в вопросы</t>
-        </is>
-      </c>
-      <c r="E103" s="19">
-        <f>COUNTA(G103:U103)</f>
-        <v/>
-      </c>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="21" t="n"/>
-      <c r="H103" s="21" t="n"/>
-      <c r="I103" s="21" t="n"/>
-      <c r="J103" s="21" t="n"/>
-      <c r="K103" s="21" t="n"/>
-      <c r="L103" s="21" t="n"/>
-      <c r="M103" s="21" t="n"/>
-      <c r="N103" s="21" t="n"/>
-      <c r="O103" s="21" t="n"/>
-      <c r="P103" s="21" t="n"/>
-      <c r="Q103" s="21" t="n"/>
-      <c r="R103" s="21" t="n"/>
-      <c r="S103" s="21" t="n"/>
-      <c r="T103" s="21" t="n"/>
-      <c r="U103" s="21" t="n"/>
-    </row>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="12" t="n"/>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>3. ИТОГ — сразу после созвона</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="n"/>
-      <c r="D104" s="12" t="n"/>
-      <c r="E104" s="12" t="n"/>
-      <c r="F104" s="12" t="n"/>
-      <c r="G104" s="12" t="n"/>
-      <c r="H104" s="12" t="n"/>
-      <c r="I104" s="12" t="n"/>
-      <c r="J104" s="12" t="n"/>
-      <c r="K104" s="12" t="n"/>
-      <c r="L104" s="12" t="n"/>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="12" t="n"/>
-      <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="12" t="n"/>
-      <c r="R104" s="12" t="n"/>
-      <c r="S104" s="12" t="n"/>
-      <c r="T104" s="12" t="n"/>
-      <c r="U104" s="12" t="n"/>
-    </row>
-    <row r="105" ht="84" customHeight="1">
-      <c r="A105" s="16" t="n"/>
-      <c r="B105" s="17" t="inlineStr">
-        <is>
-          <t>Что услышали (метки)</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>Несколько вариантов</t>
-        </is>
-      </c>
-      <c r="D105" s="18" t="inlineStr">
-        <is>
-          <t>⏳ Нет времени · 💸 Дорого · 📱 Неудобно в приложении · 🔔 Бесят пуши · 🎓 Хочет экспертов · 👭 Хочет сообщество · 🏠 Хочет офлайн · 🧘‍♀️ Любит короткие практики · 🌙 Проблемы со сном · 🤖 Нравится Ева-помощница · 💡 Идея фичи · ❤️ Готова рекомендовать</t>
-        </is>
-      </c>
-      <c r="E105" s="19">
-        <f>COUNTA(G105:U105)</f>
-        <v/>
-      </c>
-      <c r="F105" s="20" t="inlineStr">
-        <is>
-          <t>⏳ Нет времени, 🧘‍♀️ Любит короткие практики, 🔔 Бесят пуши</t>
-        </is>
-      </c>
-      <c r="G105" s="21" t="n"/>
-      <c r="H105" s="21" t="n"/>
-      <c r="I105" s="21" t="n"/>
-      <c r="J105" s="21" t="n"/>
-      <c r="K105" s="21" t="n"/>
-      <c r="L105" s="21" t="n"/>
-      <c r="M105" s="21" t="n"/>
-      <c r="N105" s="21" t="n"/>
-      <c r="O105" s="21" t="n"/>
-      <c r="P105" s="21" t="n"/>
-      <c r="Q105" s="21" t="n"/>
-      <c r="R105" s="21" t="n"/>
-      <c r="S105" s="21" t="n"/>
-      <c r="T105" s="21" t="n"/>
-      <c r="U105" s="21" t="n"/>
-    </row>
-    <row r="106" ht="58" customHeight="1">
-      <c r="A106" s="16" t="n"/>
-      <c r="B106" s="17" t="inlineStr">
-        <is>
-          <t>Главный инсайт — одной фразой</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="inlineStr">
-        <is>
-          <t>Развёрнутый ответ</t>
-        </is>
-      </c>
-      <c r="D106" s="18" t="inlineStr">
-        <is>
-          <t>Например: бросает практики, когда болеет ребёнок — нужен режим «пауза без чувства вины»</t>
-        </is>
-      </c>
-      <c r="E106" s="19">
-        <f>COUNTA(G106:U106)</f>
-        <v/>
-      </c>
-      <c r="F106" s="20" t="inlineStr">
-        <is>
-          <t>Бросает, когда пропускает пару дней и «сгорают» звёзды — нужен режим паузы без чувства вины.</t>
-        </is>
-      </c>
-      <c r="G106" s="21" t="n"/>
-      <c r="H106" s="21" t="n"/>
-      <c r="I106" s="21" t="n"/>
-      <c r="J106" s="21" t="n"/>
-      <c r="K106" s="21" t="n"/>
-      <c r="L106" s="21" t="n"/>
-      <c r="M106" s="21" t="n"/>
-      <c r="N106" s="21" t="n"/>
-      <c r="O106" s="21" t="n"/>
-      <c r="P106" s="21" t="n"/>
-      <c r="Q106" s="21" t="n"/>
-      <c r="R106" s="21" t="n"/>
-      <c r="S106" s="21" t="n"/>
-      <c r="T106" s="21" t="n"/>
-      <c r="U106" s="21" t="n"/>
-    </row>
-    <row r="107" ht="58" customHeight="1">
-      <c r="A107" s="16" t="n"/>
-      <c r="B107" s="17" t="inlineStr">
-        <is>
-          <t>Что улучшить в Еве</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
-        <is>
-          <t>Развёрнутый ответ</t>
-        </is>
-      </c>
-      <c r="D107" s="18" t="inlineStr">
-        <is>
-          <t>Идеи и просьбы</t>
-        </is>
-      </c>
-      <c r="E107" s="19">
-        <f>COUNTA(G107:U107)</f>
-        <v/>
-      </c>
-      <c r="F107" s="20" t="inlineStr">
-        <is>
-          <t>Режим «5 минут», пуши вечером, пауза для звёзд.</t>
-        </is>
-      </c>
-      <c r="G107" s="21" t="n"/>
-      <c r="H107" s="21" t="n"/>
-      <c r="I107" s="21" t="n"/>
-      <c r="J107" s="21" t="n"/>
-      <c r="K107" s="21" t="n"/>
-      <c r="L107" s="21" t="n"/>
-      <c r="M107" s="21" t="n"/>
-      <c r="N107" s="21" t="n"/>
-      <c r="O107" s="21" t="n"/>
-      <c r="P107" s="21" t="n"/>
-      <c r="Q107" s="21" t="n"/>
-      <c r="R107" s="21" t="n"/>
-      <c r="S107" s="21" t="n"/>
-      <c r="T107" s="21" t="n"/>
-      <c r="U107" s="21" t="n"/>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="16" t="n"/>
-      <c r="B108" s="17" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="inlineStr">
-        <is>
-          <t>Один вариант</t>
-        </is>
-      </c>
-      <c r="D108" s="18" t="inlineStr">
-        <is>
-          <t>Инсайты собраны · Готова помогать ещё</t>
-        </is>
-      </c>
-      <c r="E108" s="19">
-        <f>COUNTA(G108:U108)</f>
-        <v/>
-      </c>
-      <c r="F108" s="20" t="inlineStr">
-        <is>
-          <t>Инсайты собраны</t>
-        </is>
-      </c>
-      <c r="G108" s="21" t="n"/>
-      <c r="H108" s="21" t="n"/>
-      <c r="I108" s="21" t="n"/>
-      <c r="J108" s="21" t="n"/>
-      <c r="K108" s="21" t="n"/>
-      <c r="L108" s="21" t="n"/>
-      <c r="M108" s="21" t="n"/>
-      <c r="N108" s="21" t="n"/>
-      <c r="O108" s="21" t="n"/>
-      <c r="P108" s="21" t="n"/>
-      <c r="Q108" s="21" t="n"/>
-      <c r="R108" s="21" t="n"/>
-      <c r="S108" s="21" t="n"/>
-      <c r="T108" s="21" t="n"/>
-      <c r="U108" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5397,7 +4480,7 @@
     <dataValidation sqref="G52:U52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Списки!$V$1:$V$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G108:U108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G86:U86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Списки!$W$1:$W$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6216,7 +5299,7 @@
       <c r="A23" s="12" t="n"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>2. СОЗВОН — открытые вопросы для Zoom, 20–30 минут. Записывайте коротко, своими словами</t>
+          <t>2. СОЗВОН — открытые вопросы для Zoom, около 30 минут. Записывайте коротко, своими словами</t>
         </is>
       </c>
       <c r="C23" s="12" t="n"/>
@@ -7714,7 +6797,7 @@
       <c r="A19" s="12" t="n"/>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>2. ВСТРЕЧА — открытые вопросы для Zoom, 20–30 минут. Записывайте коротко, своими словами</t>
+          <t>2. ВСТРЕЧА — открытые вопросы для Zoom, около 30 минут. Записывайте коротко, своими словами</t>
         </is>
       </c>
       <c r="C19" s="12" t="n"/>
@@ -9109,7 +8192,7 @@
       <c r="A20" s="12" t="n"/>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2. СОЗВОН — открытые вопросы для Zoom, 20–30 минут. Записывайте коротко, своими словами</t>
+          <t>2. СОЗВОН — открытые вопросы для Zoom, около 30 минут. Записывайте коротко, своими словами</t>
         </is>
       </c>
       <c r="C20" s="12" t="n"/>
